--- a/output/casestudy_20260903.xlsx
+++ b/output/casestudy_20260903.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9.551197299999785</v>
+        <v>9.01425240000026</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8.841283200000362</v>
+        <v>8.963195999999698</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.273765299999923</v>
+        <v>5.270896399999401</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>10.2047806999999</v>
+        <v>9.065721200000553</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10.8974490999999</v>
+        <v>10.23402200000055</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>7.089978199999678</v>
+        <v>6.644772999999986</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.6 초</t>
+          <t>9.0 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8.8 초</t>
+          <t>9.0 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.2 초</t>
+          <t>9.1 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.9 초</t>
+          <t>10.2 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7.1 초</t>
+          <t>6.6 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>53.0 초</t>
+          <t>50.2 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260903.xlsx
+++ b/output/casestudy_20260903.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9.01425240000026</v>
+        <v>9.944106500000089</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8.963195999999698</v>
+        <v>9.178602599999977</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.270896399999401</v>
+        <v>6.197993400000087</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>9.065721200000553</v>
+        <v>9.682610299999396</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10.23402200000055</v>
+        <v>10.91517970000041</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.644772999999986</v>
+        <v>6.893882400000621</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.0 초</t>
+          <t>9.9 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.0 초</t>
+          <t>9.2 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.3 초</t>
+          <t>6.2 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.1 초</t>
+          <t>9.7 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.2 초</t>
+          <t>10.9 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.6 초</t>
+          <t>6.9 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50.2 초</t>
+          <t>54.0 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260903.xlsx
+++ b/output/casestudy_20260903.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9.944106500000089</v>
+        <v>10.99524650000058</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9.178602599999977</v>
+        <v>9.713976099999854</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.197993400000087</v>
+        <v>6.921062999999776</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>9.682610299999396</v>
+        <v>10.73079680000046</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10.91517970000041</v>
+        <v>10.54632200000015</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.893882400000621</v>
+        <v>6.520521300000837</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.9 초</t>
+          <t>11.0 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.2 초</t>
+          <t>9.7 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.2 초</t>
+          <t>6.9 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.7 초</t>
+          <t>10.7 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.9 초</t>
+          <t>10.5 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.9 초</t>
+          <t>6.5 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>54.0 초</t>
+          <t>56.6 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260903.xlsx
+++ b/output/casestudy_20260903.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10.99524650000058</v>
+        <v>9.282191899999816</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9.713976099999854</v>
+        <v>9.723907300000064</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.921062999999776</v>
+        <v>5.467972099999315</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>10.73079680000046</v>
+        <v>9.409550899999886</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10.54632200000015</v>
+        <v>9.784537300000011</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,59 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.520521300000837</v>
+        <v>6.333490700000766</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R1 용인 실측</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>general_a_2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-08-28 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>476.02327</v>
+      </c>
+      <c r="E8" t="n">
+        <v>132.28</v>
+      </c>
+      <c r="F8" t="n">
+        <v>132.28</v>
+      </c>
+      <c r="G8" t="n">
+        <v>41.08229342532648</v>
+      </c>
+      <c r="H8" t="n">
+        <v>100.8144862191238</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12448156.41290323</v>
+      </c>
+      <c r="J8" t="n">
+        <v>49597412.23</v>
+      </c>
+      <c r="K8" t="n">
+        <v>62045568.64290322</v>
+      </c>
+      <c r="L8" t="n">
+        <v>20.06292582238594</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>cache</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>11.59839840000132</v>
       </c>
     </row>
   </sheetData>
@@ -818,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1645,9 +1697,137 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>R1 용인 실측</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>132.28</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>500</v>
+      </c>
+      <c r="C27" t="n">
+        <v>653924.9987308802</v>
+      </c>
+      <c r="D27" t="n">
+        <v>28.80135248983531</v>
+      </c>
+      <c r="E27" t="n">
+        <v>465585.7548272483</v>
+      </c>
+      <c r="F27" t="n">
+        <v>120.48</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1381815.952363797</v>
+      </c>
+      <c r="H27" t="n">
+        <v>21832794.0374309</v>
+      </c>
+      <c r="I27" t="n">
+        <v>23214609.9897947</v>
+      </c>
+      <c r="J27" t="n">
+        <v>23214609.9897947</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1307849.99746176</v>
+      </c>
+      <c r="D28" t="n">
+        <v>15.68075433387349</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1102769.252304211</v>
+      </c>
+      <c r="F28" t="n">
+        <v>120.48</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1488664.996080711</v>
+      </c>
+      <c r="H28" t="n">
+        <v>23715557.01062761</v>
+      </c>
+      <c r="I28" t="n">
+        <v>25204222.00670832</v>
+      </c>
+      <c r="J28" t="n">
+        <v>25204222.00670832</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2615699.994923521</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8.179882063646165</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2401738.820199978</v>
+      </c>
+      <c r="F29" t="n">
+        <v>120.48</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1655928.939685931</v>
+      </c>
+      <c r="H29" t="n">
+        <v>24660958.77724204</v>
+      </c>
+      <c r="I29" t="n">
+        <v>26316887.71692798</v>
+      </c>
+      <c r="J29" t="n">
+        <v>26316887.71692798</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A26:A29"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A14:A17"/>
@@ -1664,7 +1844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I127"/>
+  <dimension ref="A1:I148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5308,8 +5488,607 @@
       </c>
       <c r="I127" t="inlineStr"/>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>R1 용인 실측</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>500</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>기본요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1381815.952363797</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1006429.095233478</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1589720.920636741</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>36.69146060993108</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>전력량요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>21832794.0374309</v>
+      </c>
+      <c r="E129" t="n">
+        <v>19707849.27224809</v>
+      </c>
+      <c r="F129" t="n">
+        <v>23383003.92461409</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>15.71720495884344</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>절감액(원)</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>22562082.16532806</v>
+      </c>
+      <c r="E130" t="n">
+        <v>20165934.02647321</v>
+      </c>
+      <c r="F130" t="n">
+        <v>24277784.97374577</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>16.93668080394961</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>12개월 환산 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>22562082.16532807</v>
+      </c>
+      <c r="E131" t="n">
+        <v>20165934.02647321</v>
+      </c>
+      <c r="F131" t="n">
+        <v>24277784.97374577</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>16.93668080394962</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>요금적용전력(kW)</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>120.48</v>
+      </c>
+      <c r="E132" t="n">
+        <v>120.48</v>
+      </c>
+      <c r="F132" t="n">
+        <v>122.4488373442634</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>1.607885699010822</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>발전량(kWh)</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>653924.9987308802</v>
+      </c>
+      <c r="E133" t="n">
+        <v>653917.3979531642</v>
+      </c>
+      <c r="F133" t="n">
+        <v>653931.4335780952</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>0.002146345046327881</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>회수기간(년)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>기본요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1488664.996080711</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1043277.277419355</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1771658.825806452</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>41.11296925668185</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>전력량요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>23715557.01062761</v>
+      </c>
+      <c r="E136" t="n">
+        <v>21181957.19322234</v>
+      </c>
+      <c r="F136" t="n">
+        <v>25237507.33343017</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>16.06953526204924</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>절감액(원)</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>24502814.55603168</v>
+      </c>
+      <c r="E137" t="n">
+        <v>21582041.61871959</v>
+      </c>
+      <c r="F137" t="n">
+        <v>26325870.31366242</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>18.01964622032234</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>12개월 환산 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>24502814.55603169</v>
+      </c>
+      <c r="E138" t="n">
+        <v>21582041.61871959</v>
+      </c>
+      <c r="F138" t="n">
+        <v>26325870.31366242</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>18.01964622032234</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>요금적용전력(kW)</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>120.48</v>
+      </c>
+      <c r="E139" t="n">
+        <v>120.48</v>
+      </c>
+      <c r="F139" t="n">
+        <v>121.88</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>1.148670823761069</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>발전량(kWh)</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1307849.99746176</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1307834.795906328</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1307862.86715619</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>0.002146345046327881</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>회수기간(년)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>기본요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1655928.939685931</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1043277.277419355</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1771658.825806452</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>41.11296925668185</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>전력량요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>24660958.77724204</v>
+      </c>
+      <c r="E143" t="n">
+        <v>21975745.48019315</v>
+      </c>
+      <c r="F143" t="n">
+        <v>25876114.84618873</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>15.07324182621669</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>절감액(원)</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>25626185.15864207</v>
+      </c>
+      <c r="E144" t="n">
+        <v>22319085.09248485</v>
+      </c>
+      <c r="F144" t="n">
+        <v>26964477.82642099</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>17.22782382006443</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>12개월 환산 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>25626185.15864207</v>
+      </c>
+      <c r="E145" t="n">
+        <v>22319085.09248485</v>
+      </c>
+      <c r="F145" t="n">
+        <v>26964477.82642099</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>17.22782382006443</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>요금적용전력(kW)</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>120.48</v>
+      </c>
+      <c r="E146" t="n">
+        <v>120.48</v>
+      </c>
+      <c r="F146" t="n">
+        <v>121.88</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>1.148670823761069</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>발전량(kWh)</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>2615699.994923521</v>
+      </c>
+      <c r="E147" t="n">
+        <v>2615669.591812657</v>
+      </c>
+      <c r="F147" t="n">
+        <v>2615725.734312381</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>0.002146345046327881</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>회수기간(년)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="28">
     <mergeCell ref="A44:A64"/>
     <mergeCell ref="B86:B92"/>
     <mergeCell ref="B44:B50"/>
@@ -5318,13 +6097,17 @@
     <mergeCell ref="A23:A43"/>
     <mergeCell ref="B107:B113"/>
     <mergeCell ref="B37:B43"/>
+    <mergeCell ref="B128:B134"/>
     <mergeCell ref="B65:B71"/>
     <mergeCell ref="A107:A127"/>
+    <mergeCell ref="B142:B148"/>
+    <mergeCell ref="A128:A148"/>
     <mergeCell ref="B16:B22"/>
     <mergeCell ref="B30:B36"/>
     <mergeCell ref="B114:B120"/>
     <mergeCell ref="B79:B85"/>
     <mergeCell ref="B51:B57"/>
+    <mergeCell ref="B135:B141"/>
     <mergeCell ref="A65:A85"/>
     <mergeCell ref="A86:A106"/>
     <mergeCell ref="B72:B78"/>
@@ -5345,7 +6128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5693,12 +6476,82 @@
         <v>0</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>R1 용인 실측</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>62965205.72874191</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-919637.0858386904</v>
+      </c>
+      <c r="E20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>62045568.64290322</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>68897825.82974194</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-6852257.186838716</v>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>68324412.09090322</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-6278843.447999999</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A20:A23"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A14:A16"/>
   </mergeCells>
@@ -5712,7 +6565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6415,14 +7268,125 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>R1 용인 실측</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>7.1 선택요금 전환</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>II → II</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>7.2 계약전력 조정</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>계약 290 kW (실제 값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>7.4 역률 개선 (92→97%)</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>124481.5641290322</v>
+      </c>
+      <c r="D34" t="n">
+        <v>124481.5641290322</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>요금표와 약관만으로 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>7.6 ESS</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>중간~낮음</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>최소 규격 미달 — 필요 출력 25.3 kW &lt; 상업용 최소 50 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>7.3 경제성DR</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>거래 가능일 244일 · 등록 권장 28 kW · 연간 감축 5,882 kWh</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A22:A26"/>
     <mergeCell ref="A17:A21"/>
     <mergeCell ref="A12:A16"/>
     <mergeCell ref="A27:A31"/>
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A32:A36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6434,7 +7398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7920,12 +8884,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>교차</t>
+          <t>R1 용인 실측</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>C1 오전 피크형 &gt; C2 오후 피크형 (요금적용전력 저감 폭)</t>
+          <t>PV 0 kWp 절감액이 정확히 0</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -7935,14 +8899,14 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>C1 95.4 kW vs C2 5.8 kW — C2 는 피크가 늦어 PV 가 깎은 뒤 저녁 슬롯이 새 최대가 된다</t>
+          <t>0.000000 원</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="inlineStr">
         <is>
-          <t>C3 평탄형은 기본요금 절감이 거의 없다 (절감의 대부분이 전력량요금)</t>
+          <t>용량 증가 시 전력량요금 절감액 단조 증가</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -7952,14 +8916,14 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>기본요금 비중 C3 3.6% vs C1 10.2% (C3 저감 26.1 kW)</t>
+          <t>0 → 21,832,794 → 23,715,557 → 24,660,959</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="inlineStr">
         <is>
-          <t>C5 겨울 피크형은 기본요금 절감이 매우 작다</t>
+          <t>기본요금 절감액 단조 증가 후 포화</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -7969,14 +8933,14 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>저감률 C5 0.28% vs C1 1.80% — 겨울 대상월의 피크가 07~09시·17~20시라 PV 가 닿지 않는다</t>
+          <t>증분 1,381,816 → 106,849 → 167,264</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="inlineStr">
         <is>
-          <t>C6 야간 피크형: 요금적용전력 &lt; 관측 최대수요 (경부하 제외, 5.2 ①)</t>
+          <t>용량 증가 시 요금적용전력 단조 감소</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -7986,14 +8950,14 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>관측 10,920.6 kW vs 요금적용 2,801.0 kW (74.4% 낮다)</t>
+          <t>132.3 → 120.5 → 120.5 → 120.5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="inlineStr">
         <is>
-          <t>C6 야간 피크형의 PV 기여가 오히려 크다 (저감률)</t>
+          <t>감도 세 시나리오의 발전량이 ±1% 이내 (총량 보존)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -8003,34 +8967,278 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>저감률 C6 3.05% vs C1 1.80% — 대상 슬롯이 주간뿐이라 PV 가 그대로 듣는다</t>
+          <t>최대 편차 0.002%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="inlineStr">
         <is>
+          <t>기준값이 범위 안에 있음</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>벗어난 지표 0건</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>상한 시나리오 기록 (단조성은 요구하지 않는다)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>기본요금 절감액 상한: 평탄형</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>선택요금 전환 절감액 ≥ 0 (확정 계산)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>0 원 · II → II</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>역률 개선 절감액 = 기본요금의 1.0% (감액 상한)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>124,482 원 (기본요금 12,448,156 의 1.00%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>DR 거래 가능일이 전체 일수보다 적음 (토·일·공휴일 제외)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>244 / 365일</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ESS 성립하지 않으면 목표가 0 (없는 목표를 내지 않는다)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>viable=False · 목표 0 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ESS 목표를 냈으면 절감액 &gt; 0</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>목표 0 kW · 절감액 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ESS 목표 달성이면 실제 요금적용전력이 목표 이하</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>어긋난 점 0개 / 0개</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ESS 절감액이 0 이하인 점에는 회수기간이 없다</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>어긋난 점 0개 / 0개</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>교차</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>C1 오전 피크형 &gt; C2 오후 피크형 (요금적용전력 저감 폭)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>C1 95.4 kW vs C2 5.8 kW — C2 는 피크가 늦어 PV 가 깎은 뒤 저녁 슬롯이 새 최대가 된다</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>C3 평탄형은 기본요금 절감이 거의 없다 (절감의 대부분이 전력량요금)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>기본요금 비중 C3 3.6% vs C1 10.2% (C3 저감 26.1 kW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>C5 겨울 피크형은 기본요금 절감이 매우 작다</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>저감률 C5 0.28% vs C1 1.80% — 겨울 대상월의 피크가 07~09시·17~20시라 PV 가 닿지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>C6 야간 피크형: 요금적용전력 &lt; 관측 최대수요 (경부하 제외, 5.2 ①)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>관측 10,920.6 kW vs 요금적용 2,801.0 kW (74.4% 낮다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>C6 야간 피크형의 PV 기여가 오히려 크다 (저감률)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>저감률 C6 3.05% vs C1 1.80% — 대상 슬롯이 주간뿐이라 PV 가 그대로 듣는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
           <t>C4 산업용(을) 주말 할인이 PV 최성기와 겹쳐 전력량요금 절감 비율이 낮다</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
         <is>
           <t>C4 4.95% vs C1 5.44% (봄·가을 토·일·공휴일 11~14시 할인 구간의 단가가 이미 낮다)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A30:A43"/>
     <mergeCell ref="A44:A57"/>
     <mergeCell ref="A16:A29"/>
-    <mergeCell ref="A86:A91"/>
     <mergeCell ref="A72:A85"/>
+    <mergeCell ref="A86:A99"/>
+    <mergeCell ref="A100:A105"/>
     <mergeCell ref="A2:A15"/>
     <mergeCell ref="A58:A71"/>
   </mergeCells>
@@ -8044,7 +9252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8067,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11.0 초</t>
+          <t>9.3 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.9 초</t>
+          <t>5.5 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.7 초</t>
+          <t>9.4 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.5 초</t>
+          <t>9.8 초</t>
         </is>
       </c>
     </row>
@@ -8127,43 +9335,55 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.5 초</t>
+          <t>6.3 초</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>전체 소요</t>
+          <t>R1 용인 실측 소요</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>56.6 초</t>
+          <t>11.6 초</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>기상 취득 호출</t>
+          <t>전체 소요</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0 회</t>
+          <t>65.0 초</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>기상 취득 호출</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0 회</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>기상 캐시 적중</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>6/6 (모든 케이스가 같은 좌표·기간이라 첫 건만 취득한다)</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7/7 (합성 여섯은 좌표·기간이 같아 첫 건만 취득한다. 실측은 따로 선다)</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260903.xlsx
+++ b/output/casestudy_20260903.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9.282191899999816</v>
+        <v>8.100723100000323</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9.723907300000064</v>
+        <v>8.003625500001363</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.467972099999315</v>
+        <v>4.843560900000739</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>9.409550899999886</v>
+        <v>8.302643200000603</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>9.784537300000011</v>
+        <v>8.968809600000895</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.333490700000766</v>
+        <v>5.727085799999259</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11.59839840000132</v>
+        <v>10.91275359999963</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.3 초</t>
+          <t>8.1 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.7 초</t>
+          <t>8.0 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.5 초</t>
+          <t>4.8 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.4 초</t>
+          <t>8.3 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9.8 초</t>
+          <t>9.0 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.3 초</t>
+          <t>5.7 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11.6 초</t>
+          <t>10.9 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>65.0 초</t>
+          <t>57.8 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260903.xlsx
+++ b/output/casestudy_20260903.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8.100723100000323</v>
+        <v>9.678451199997653</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8.003625500001363</v>
+        <v>10.2896096000004</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.843560900000739</v>
+        <v>6.108942200000456</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>8.302643200000603</v>
+        <v>10.69667610000033</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>8.968809600000895</v>
+        <v>10.77970809999897</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.727085799999259</v>
+        <v>6.472135399999388</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>10.91275359999963</v>
+        <v>14.44588410000142</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8.1 초</t>
+          <t>9.7 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8.0 초</t>
+          <t>10.3 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.8 초</t>
+          <t>6.1 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.3 초</t>
+          <t>10.7 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9.0 초</t>
+          <t>10.8 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.7 초</t>
+          <t>6.5 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.9 초</t>
+          <t>14.4 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>57.8 초</t>
+          <t>71.8 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260903.xlsx
+++ b/output/casestudy_20260903.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9.678451199997653</v>
+        <v>8.382639700001164</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10.2896096000004</v>
+        <v>8.172449300000153</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.108942200000456</v>
+        <v>5.136070299999119</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>10.69667610000033</v>
+        <v>8.811009199998807</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10.77970809999897</v>
+        <v>8.957527300000947</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.472135399999388</v>
+        <v>5.786643400002504</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>14.44588410000142</v>
+        <v>11.46823899999799</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.7 초</t>
+          <t>8.4 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.3 초</t>
+          <t>8.2 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.1 초</t>
+          <t>5.1 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.7 초</t>
+          <t>8.8 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.8 초</t>
+          <t>9.0 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.5 초</t>
+          <t>5.8 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14.4 초</t>
+          <t>11.5 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>71.8 초</t>
+          <t>59.8 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260903.xlsx
+++ b/output/casestudy_20260903.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8.382639700001164</v>
+        <v>8.726467200001935</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8.172449300000153</v>
+        <v>8.684545700001763</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.136070299999119</v>
+        <v>5.122102299999824</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>8.811009199998807</v>
+        <v>8.97673020000002</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>8.957527300000947</v>
+        <v>9.630334200002835</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.786643400002504</v>
+        <v>7.02917829999933</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11.46823899999799</v>
+        <v>12.87224040000001</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8.4 초</t>
+          <t>8.7 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8.2 초</t>
+          <t>8.7 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.8 초</t>
+          <t>9.0 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9.0 초</t>
+          <t>9.6 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.8 초</t>
+          <t>7.0 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11.5 초</t>
+          <t>12.9 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>59.8 초</t>
+          <t>64.9 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260903.xlsx
+++ b/output/casestudy_20260903.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8.726467200001935</v>
+        <v>9.290942800002085</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8.684545700001763</v>
+        <v>8.944050199999765</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.122102299999824</v>
+        <v>5.33356890000141</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>8.97673020000002</v>
+        <v>9.737486599999102</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>9.630334200002835</v>
+        <v>10.79151540000021</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>7.02917829999933</v>
+        <v>6.307829600002151</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>12.87224040000001</v>
+        <v>12.0364327999996</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8.7 초</t>
+          <t>9.3 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8.7 초</t>
+          <t>8.9 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.1 초</t>
+          <t>5.3 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.0 초</t>
+          <t>9.7 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9.6 초</t>
+          <t>10.8 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7.0 초</t>
+          <t>6.3 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12.9 초</t>
+          <t>12.0 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>64.9 초</t>
+          <t>65.8 초</t>
         </is>
       </c>
     </row>
